--- a/erp-server/erp-server-file/src/main/resources/excel/srm/poReconciliationDetail.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/srm/poReconciliationDetail.xlsx
@@ -1,15 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>单据单号</t>
   </si>
@@ -37,6 +35,12 @@
     <t>采购单号</t>
   </si>
   <si>
+    <t>送货单号</t>
+  </si>
+  <si>
+    <t>对账状态</t>
+  </si>
+  <si>
     <t>单据类型</t>
   </si>
   <si>
@@ -46,7 +50,7 @@
     <t>业务状态</t>
   </si>
   <si>
-    <t>确认日期</t>
+    <t>单据日期</t>
   </si>
   <si>
     <t>SKU</t>
@@ -55,10 +59,7 @@
     <t>产品名称</t>
   </si>
   <si>
-    <t>送货数量</t>
-  </si>
-  <si>
-    <t>收货数量</t>
+    <t>数量</t>
   </si>
   <si>
     <t>税率</t>
@@ -79,7 +80,7 @@
     <t>付款条件</t>
   </si>
   <si>
-    <t>是否加入账单</t>
+    <t>单据备注</t>
   </si>
   <si>
     <t>{.sourceCode}</t>
@@ -88,6 +89,12 @@
     <t>{.poCode}</t>
   </si>
   <si>
+    <t>{.deliveryCode}</t>
+  </si>
+  <si>
+    <t>{.statusName}</t>
+  </si>
+  <si>
     <t>{.sourceTypeName}</t>
   </si>
   <si>
@@ -97,7 +104,7 @@
     <t>{.businessStatusName}</t>
   </si>
   <si>
-    <t>{.confirmDate}</t>
+    <t>{.date}</t>
   </si>
   <si>
     <t>{.skuNo}</t>
@@ -106,10 +113,7 @@
     <t>{.productName}</t>
   </si>
   <si>
-    <t>{.deliveryQty}</t>
-  </si>
-  <si>
-    <t>{.receiveQty}</t>
+    <t>{.qty}</t>
   </si>
   <si>
     <t>{.taxRateStr}</t>
@@ -130,7 +134,7 @@
     <t>{.paymentConditionName}</t>
   </si>
   <si>
-    <t>{.isAddAccountStr}</t>
+    <t>{.remark}</t>
   </si>
 </sst>
 </file>
@@ -809,6 +813,13 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1061,27 +1072,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="14.125" customWidth="1"/>
-    <col min="3" max="3" width="15.375" customWidth="1"/>
-    <col min="4" max="4" width="20.25" customWidth="1"/>
-    <col min="5" max="5" width="15.625" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="15.25" customWidth="1"/>
-    <col min="8" max="8" width="18.5" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="14.5" customWidth="1"/>
-    <col min="11" max="12" width="12.125" customWidth="1"/>
-    <col min="13" max="13" width="14.875" customWidth="1"/>
-    <col min="14" max="14" width="21.875" customWidth="1"/>
-    <col min="15" max="15" width="15.375" customWidth="1"/>
-    <col min="16" max="16" width="17.625" customWidth="1"/>
+    <col min="3" max="4" width="18.25" customWidth="1"/>
+    <col min="5" max="5" width="15.375" customWidth="1"/>
+    <col min="6" max="6" width="20.25" customWidth="1"/>
+    <col min="7" max="7" width="15.625" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="15.25" customWidth="1"/>
+    <col min="10" max="10" width="18.5" customWidth="1"/>
+    <col min="11" max="11" width="14.5" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
+    <col min="13" max="13" width="12.125" customWidth="1"/>
+    <col min="14" max="14" width="14.875" customWidth="1"/>
+    <col min="15" max="15" width="21.875" customWidth="1"/>
+    <col min="16" max="16" width="19.75" customWidth="1"/>
+    <col min="17" max="17" width="22.375" customWidth="1"/>
+    <col min="18" max="18" width="17.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1133,58 +1146,64 @@
       <c r="Q1" t="s">
         <v>16</v>
       </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1192,28 +1211,4 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/erp-server/erp-server-file/src/main/resources/excel/srm/poReconciliationDetail.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/srm/poReconciliationDetail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
-    <t>单据单号</t>
+    <t>单据编号</t>
   </si>
   <si>
     <t>采购单号</t>
@@ -813,13 +813,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
